--- a/output/sliding_window_results_window_2.xlsx
+++ b/output/sliding_window_results_window_2.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>29.54</v>
+        <v>33.1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.30519755058803</v>
+        <v>33.54059187866695</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.234802449411966</v>
+        <v>0.4405918786669503</v>
       </c>
       <c r="E2" t="n">
-        <v>10.46394688672165</v>
+        <v>0.1941212035472726</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>29.81</v>
+        <v>34.4</v>
       </c>
       <c r="C3" t="n">
-        <v>28.00641501647322</v>
+        <v>35.58911771635769</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.803584983526779</v>
+        <v>1.189117716357693</v>
       </c>
       <c r="E3" t="n">
-        <v>3.252918792803292</v>
+        <v>1.414000943355734</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>30.21</v>
+        <v>36.3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.75328243122379</v>
+        <v>36.97379569471273</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.456717568776206</v>
+        <v>0.6737956947127373</v>
       </c>
       <c r="E4" t="n">
-        <v>6.035461212733672</v>
+        <v>0.4540006382134202</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>30.48</v>
+        <v>38.5</v>
       </c>
       <c r="C5" t="n">
-        <v>28.89904831782838</v>
+        <v>40.09845880947552</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.580951682171619</v>
+        <v>1.598458809475517</v>
       </c>
       <c r="E5" t="n">
-        <v>2.499408221361273</v>
+        <v>2.555070565589886</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>30.95</v>
+        <v>40.1</v>
       </c>
       <c r="C6" t="n">
-        <v>29.93289017436372</v>
+        <v>43.5812084081156</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.017109825636279</v>
+        <v>3.481208408115599</v>
       </c>
       <c r="E6" t="n">
-        <v>1.034512397405862</v>
+        <v>12.11881198073474</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>31.38</v>
+        <v>41.5</v>
       </c>
       <c r="C7" t="n">
-        <v>31.14190973140312</v>
+        <v>45.98305223987234</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2380902685968813</v>
+        <v>4.483052239872336</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05668697600053509</v>
+        <v>20.09775738542437</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.01613277762396</v>
+        <v>48.60998047298623</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2638672223760423</v>
+        <v>4.909980472986227</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06962591104444776</v>
+        <v>24.10790824510605</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C9" t="n">
-        <v>31.54677352012715</v>
+        <v>52.31003760819778</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.553226479872855</v>
+        <v>4.21003760819778</v>
       </c>
       <c r="E9" t="n">
-        <v>2.41251249777822</v>
+        <v>17.72441666243968</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>32.7095020702765</v>
+        <v>56.81746979049109</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.690497929723499</v>
+        <v>3.817469790491089</v>
       </c>
       <c r="E10" t="n">
-        <v>2.857783250399435</v>
+        <v>14.57307560131208</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C11" t="n">
-        <v>34.21705870022907</v>
+        <v>62.00902643868139</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.08294129977093</v>
+        <v>5.909026438681387</v>
       </c>
       <c r="E11" t="n">
-        <v>4.338644458291411</v>
+        <v>34.91659345303564</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C12" t="n">
-        <v>35.77656414145579</v>
+        <v>63.74375714045158</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.723435858544214</v>
+        <v>3.743757140451578</v>
       </c>
       <c r="E12" t="n">
-        <v>7.417102875604459</v>
+        <v>14.01571752668218</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C13" t="n">
-        <v>38.24183478488062</v>
+        <v>70.51459250371076</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.858165215119385</v>
+        <v>6.61459250371076</v>
       </c>
       <c r="E13" t="n">
-        <v>3.45277796667967</v>
+        <v>43.75283399014658</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>39.76390383940034</v>
+        <v>76.1178067469193</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.736096160599665</v>
+        <v>5.517806746919305</v>
       </c>
       <c r="E14" t="n">
-        <v>3.014029878848898</v>
+        <v>30.44619129634821</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>42.186920652704</v>
+        <v>83.62737118608915</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.513079347296006</v>
+        <v>2.727371186089144</v>
       </c>
       <c r="E15" t="n">
-        <v>2.289409111213709</v>
+        <v>7.438553586709303</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>46.18833719329935</v>
+        <v>85.75869078023096</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.911662806700647</v>
+        <v>-3.34130921976903</v>
       </c>
       <c r="E16" t="n">
-        <v>3.654454686522597</v>
+        <v>11.16434730211353</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C17" t="n">
-        <v>51.72184563963598</v>
+        <v>87.04344197369498</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.27815436036402</v>
+        <v>-7.956558026305018</v>
       </c>
       <c r="E17" t="n">
-        <v>1.633678568917558</v>
+        <v>63.30681562595881</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C18" t="n">
-        <v>53.64788058239041</v>
+        <v>98.0919156237545</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.452119417609595</v>
+        <v>-0.7080843762454947</v>
       </c>
       <c r="E18" t="n">
-        <v>6.012889638218017</v>
+        <v>0.5013834838829713</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C19" t="n">
-        <v>57.15276159843812</v>
+        <v>102.4938743972061</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.847238401561881</v>
+        <v>-0.8061256027939407</v>
       </c>
       <c r="E19" t="n">
-        <v>8.106766515328658</v>
+        <v>0.6498384874798944</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C20" t="n">
-        <v>59.19205811675615</v>
+        <v>111.9081283933522</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.707941883243848</v>
+        <v>4.908128393352172</v>
       </c>
       <c r="E20" t="n">
-        <v>22.16471677600163</v>
+        <v>24.08972432562977</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C21" t="n">
-        <v>67.91188646567301</v>
+        <v>122.3410944614733</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.688113534326988</v>
+        <v>13.64109446147332</v>
       </c>
       <c r="E21" t="n">
-        <v>7.225954373431929</v>
+        <v>186.079458106838</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-39.63779669522931</v>
+        <v>55.05341226444011</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>97.99328099530693</v>
+        <v>509.6006204105481</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>4.899664049765347</v>
+        <v>25.48003102052741</v>
       </c>
     </row>
   </sheetData>
